--- a/assets/data/imf/excel/ove_pib_fmi_pppgdp_precios_corrientes_ppa_dolares_internacionales.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_pppgdp_precios_corrientes_ppa_dolares_internacionales.xlsx
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/excel/ove_pib_fmi_pppgdp_precios_corrientes_ppa_dolares_internacionales.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_pppgdp_precios_corrientes_ppa_dolares_internacionales.xlsx
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/excel/ove_pib_fmi_pppgdp_precios_corrientes_ppa_dolares_internacionales.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_pppgdp_precios_corrientes_ppa_dolares_internacionales.xlsx
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>

--- a/assets/data/imf/excel/ove_pib_fmi_pppgdp_precios_corrientes_ppa_dolares_internacionales.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_pppgdp_precios_corrientes_ppa_dolares_internacionales.xlsx
@@ -656,7 +656,7 @@
         <v>1980</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>118831734000</v>
+        <v>118318761000</v>
       </c>
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -720,7 +720,7 @@
         <v>1981</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>128398876000</v>
+        <v>127844603000</v>
       </c>
       <c r="I8" s="4" t="inlineStr"/>
       <c r="J8" s="4" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -784,7 +784,7 @@
         <v>1982</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>139938816000</v>
+        <v>139334728000</v>
       </c>
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -848,7 +848,7 @@
         <v>1983</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>131086865000</v>
+        <v>130520989000</v>
       </c>
       <c r="I10" s="4" t="inlineStr"/>
       <c r="J10" s="4" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -912,7 +912,7 @@
         <v>1984</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>142911778000</v>
+        <v>142294856000</v>
       </c>
       <c r="I11" s="4" t="inlineStr"/>
       <c r="J11" s="4" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -976,7 +976,7 @@
         <v>1985</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>148709803000</v>
+        <v>148067852000</v>
       </c>
       <c r="I12" s="4" t="inlineStr"/>
       <c r="J12" s="4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -1040,7 +1040,7 @@
         <v>1986</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>160927146000</v>
+        <v>160232455000</v>
       </c>
       <c r="I13" s="4" t="inlineStr"/>
       <c r="J13" s="4" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -1104,7 +1104,7 @@
         <v>1987</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>172832739000</v>
+        <v>172086654000</v>
       </c>
       <c r="I14" s="4" t="inlineStr"/>
       <c r="J14" s="4" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
@@ -1168,7 +1168,7 @@
         <v>1988</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>190576653000</v>
+        <v>189753971000</v>
       </c>
       <c r="I15" s="4" t="inlineStr"/>
       <c r="J15" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1232,7 +1232,7 @@
         <v>1989</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>170481950000</v>
+        <v>169746013000</v>
       </c>
       <c r="I16" s="4" t="inlineStr"/>
       <c r="J16" s="4" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -1296,7 +1296,7 @@
         <v>1990</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>188301212000</v>
+        <v>187488352000</v>
       </c>
       <c r="I17" s="4" t="inlineStr"/>
       <c r="J17" s="4" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -1360,7 +1360,7 @@
         <v>1991</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>213611605000</v>
+        <v>212689486000</v>
       </c>
       <c r="I18" s="4" t="inlineStr"/>
       <c r="J18" s="4" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -1424,7 +1424,7 @@
         <v>1992</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>231720372000</v>
+        <v>230720080000</v>
       </c>
       <c r="I19" s="4" t="inlineStr"/>
       <c r="J19" s="4" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -1488,7 +1488,7 @@
         <v>1993</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>237865576000</v>
+        <v>236838756000</v>
       </c>
       <c r="I20" s="4" t="inlineStr"/>
       <c r="J20" s="4" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -1552,7 +1552,7 @@
         <v>1994</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>237237519000</v>
+        <v>236213411000</v>
       </c>
       <c r="I21" s="4" t="inlineStr"/>
       <c r="J21" s="4" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -1616,7 +1616,7 @@
         <v>1995</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>251782239000</v>
+        <v>250695345000</v>
       </c>
       <c r="I22" s="4" t="inlineStr"/>
       <c r="J22" s="4" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
@@ -1680,7 +1680,7 @@
         <v>1996</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>255884638000</v>
+        <v>254780034000</v>
       </c>
       <c r="I23" s="4" t="inlineStr"/>
       <c r="J23" s="4" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -1744,7 +1744,7 @@
         <v>1997</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>276880619000</v>
+        <v>275685380000</v>
       </c>
       <c r="I24" s="4" t="inlineStr"/>
       <c r="J24" s="4" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
@@ -1808,7 +1808,7 @@
         <v>1998</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>280816075000</v>
+        <v>279603847000</v>
       </c>
       <c r="I25" s="4" t="inlineStr"/>
       <c r="J25" s="4" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
@@ -1872,7 +1872,7 @@
         <v>1999</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>267786443000</v>
+        <v>266630461000</v>
       </c>
       <c r="I26" s="4" t="inlineStr"/>
       <c r="J26" s="4" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
@@ -1936,7 +1936,7 @@
         <v>2000</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>283949149000</v>
+        <v>282723397000</v>
       </c>
       <c r="I27" s="4" t="inlineStr"/>
       <c r="J27" s="4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -2000,7 +2000,7 @@
         <v>2001</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>300197520000</v>
+        <v>298901626000</v>
       </c>
       <c r="I28" s="4" t="inlineStr"/>
       <c r="J28" s="4" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
@@ -2064,7 +2064,7 @@
         <v>2002</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>277865131000</v>
+        <v>276665642000</v>
       </c>
       <c r="I29" s="4" t="inlineStr"/>
       <c r="J29" s="4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
@@ -2128,7 +2128,7 @@
         <v>2003</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>261376085000</v>
+        <v>260247775000</v>
       </c>
       <c r="I30" s="4" t="inlineStr"/>
       <c r="J30" s="4" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
@@ -2192,7 +2192,7 @@
         <v>2004</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>317486193000</v>
+        <v>316115667000</v>
       </c>
       <c r="I31" s="4" t="inlineStr"/>
       <c r="J31" s="4" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
@@ -2256,7 +2256,7 @@
         <v>2005</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>361227174000</v>
+        <v>359667827000</v>
       </c>
       <c r="I32" s="4" t="inlineStr"/>
       <c r="J32" s="4" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
@@ -2320,7 +2320,7 @@
         <v>2006</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>409127619000</v>
+        <v>407361495000</v>
       </c>
       <c r="I33" s="4" t="inlineStr"/>
       <c r="J33" s="4" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
@@ -2384,7 +2384,7 @@
         <v>2007</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>456995579000</v>
+        <v>455022819000</v>
       </c>
       <c r="I34" s="4" t="inlineStr"/>
       <c r="J34" s="4" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
@@ -2448,7 +2448,7 @@
         <v>2008</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>490383395000</v>
+        <v>478984032000</v>
       </c>
       <c r="I35" s="4" t="inlineStr"/>
       <c r="J35" s="4" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -2512,7 +2512,7 @@
         <v>2009</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>477607385000</v>
+        <v>462198623000</v>
       </c>
       <c r="I36" s="4" t="inlineStr"/>
       <c r="J36" s="4" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
@@ -2576,7 +2576,7 @@
         <v>2010</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>476215106000</v>
+        <v>464719088000</v>
       </c>
       <c r="I37" s="4" t="inlineStr"/>
       <c r="J37" s="4" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
@@ -2640,7 +2640,7 @@
         <v>2011</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>506339730000</v>
+        <v>487250975000</v>
       </c>
       <c r="I38" s="4" t="inlineStr"/>
       <c r="J38" s="4" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
@@ -2704,7 +2704,7 @@
         <v>2012</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>544784286000</v>
+        <v>517383742000</v>
       </c>
       <c r="I39" s="4" t="inlineStr"/>
       <c r="J39" s="4" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
@@ -2768,7 +2768,7 @@
         <v>2013</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>561498041000</v>
+        <v>526598558000</v>
       </c>
       <c r="I40" s="4" t="inlineStr"/>
       <c r="J40" s="4" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
@@ -2832,7 +2832,7 @@
         <v>2014</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>549029973000</v>
+        <v>523416571000</v>
       </c>
       <c r="I41" s="4" t="inlineStr"/>
       <c r="J41" s="4" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
@@ -2896,7 +2896,7 @@
         <v>2015</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>519651075000</v>
+        <v>507836702000</v>
       </c>
       <c r="I42" s="4" t="inlineStr"/>
       <c r="J42" s="4" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
@@ -2960,7 +2960,7 @@
         <v>2016</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>435197214000</v>
+        <v>425622394000</v>
       </c>
       <c r="I43" s="4" t="inlineStr"/>
       <c r="J43" s="4" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
@@ -3024,7 +3024,7 @@
         <v>2017</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>373568167000</v>
+        <v>370770454000</v>
       </c>
       <c r="I44" s="4" t="inlineStr"/>
       <c r="J44" s="4" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
@@ -3088,7 +3088,7 @@
         <v>2018</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>307017686000</v>
+        <v>298117187000</v>
       </c>
       <c r="I45" s="4" t="inlineStr"/>
       <c r="J45" s="4" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
@@ -3152,7 +3152,7 @@
         <v>2019</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>225768945000</v>
+        <v>215182880000</v>
       </c>
       <c r="I46" s="4" t="inlineStr"/>
       <c r="J46" s="4" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
@@ -3216,7 +3216,7 @@
         <v>2020</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>160166576000</v>
+        <v>145666660000</v>
       </c>
       <c r="I47" s="4" t="inlineStr"/>
       <c r="J47" s="4" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
@@ -3280,7 +3280,7 @@
         <v>2021</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>169075379000</v>
+        <v>153968110000</v>
       </c>
       <c r="I48" s="4" t="inlineStr"/>
       <c r="J48" s="4" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M48" s="4" t="inlineStr">
@@ -3344,7 +3344,7 @@
         <v>2022</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>195590431000</v>
+        <v>189877918000</v>
       </c>
       <c r="I49" s="4" t="inlineStr"/>
       <c r="J49" s="4" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
@@ -3408,7 +3408,7 @@
         <v>2023</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>210943855000</v>
+        <v>208206259000</v>
       </c>
       <c r="I50" s="4" t="inlineStr"/>
       <c r="J50" s="4" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
@@ -3472,7 +3472,7 @@
         <v>2024</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>227633187000</v>
+        <v>232505079000</v>
       </c>
       <c r="I51" s="4" t="inlineStr"/>
       <c r="J51" s="4" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
@@ -3536,7 +3536,7 @@
         <v>2025</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>237678893000</v>
+        <v>260132528000</v>
       </c>
       <c r="I52" s="4" t="inlineStr"/>
       <c r="J52" s="4" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr">
@@ -3600,7 +3600,7 @@
         <v>2026</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>254371862000</v>
+        <v>282366216000</v>
       </c>
       <c r="I53" s="4" t="inlineStr"/>
       <c r="J53" s="4" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
@@ -3664,7 +3664,7 @@
         <v>2027</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>275547798000</v>
+        <v>311775906000</v>
       </c>
       <c r="I54" s="4" t="inlineStr"/>
       <c r="J54" s="4" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/25/2026</t>
         </is>
       </c>
       <c r="M54" s="4" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>275547798000</v>
+        <v>311775906000</v>
       </c>
     </row>
     <row r="18">

--- a/assets/data/imf/excel/ove_pib_fmi_pppgdp_precios_corrientes_ppa_dolares_internacionales.xlsx
+++ b/assets/data/imf/excel/ove_pib_fmi_pppgdp_precios_corrientes_ppa_dolares_internacionales.xlsx
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
